--- a/rules/examples/Advanced Despatch Advice use cases/AdvancedDespatchAdvice__Example_UseCase_02_Precast_concrete_element.xlsx
+++ b/rules/examples/Advanced Despatch Advice use cases/AdvancedDespatchAdvice__Example_UseCase_02_Precast_concrete_element.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beastab.sharepoint.com/sites/BEAstAnlggningsutskott/Shared Documents/General/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RikardLarsson\source\repos\BEAst-AB\beast-supply\rules\examples\Advanced Despatch Advice use cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{DB0BE999-383B-4ADA-B1F8-AEE0A5D4E5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57DB8AF8-404A-4382-A092-3686B22DAAA2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B48C48B-7CF4-49DB-AA52-3CBB2EFBBDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="13403" windowWidth="21795" windowHeight="12975" xr2:uid="{4FE9990F-C65C-4512-A4C9-FBC7EC8C3262}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{4FE9990F-C65C-4512-A4C9-FBC7EC8C3262}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="3" r:id="rId1"/>
@@ -72,7 +72,7 @@
     Behöver inte ha med denna men kan skicka med det om entreprenörerna vill.</t>
       </text>
     </comment>
-    <comment ref="A10" authorId="2" shapeId="0" xr:uid="{B54A39DE-43A5-43E4-8551-D38ABB14315B}">
+    <comment ref="A9" authorId="2" shapeId="0" xr:uid="{B54A39DE-43A5-43E4-8551-D38ABB14315B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -80,7 +80,7 @@
     Behöver komma överens i projektet vilken adress-rad man ska använda.</t>
       </text>
     </comment>
-    <comment ref="A15" authorId="3" shapeId="0" xr:uid="{3D75DFE4-9945-4CD7-B835-1AB81FDE3917}">
+    <comment ref="A14" authorId="3" shapeId="0" xr:uid="{3D75DFE4-9945-4CD7-B835-1AB81FDE3917}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -88,7 +88,7 @@
     Behöver vara obligatorisk</t>
       </text>
     </comment>
-    <comment ref="A20" authorId="4" shapeId="0" xr:uid="{21029AF8-9FD7-40BA-AF0F-C67FA4AF6DED}">
+    <comment ref="A19" authorId="4" shapeId="0" xr:uid="{21029AF8-9FD7-40BA-AF0F-C67FA4AF6DED}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -96,7 +96,7 @@
     Relevant kontaktperson , inte nödvändigtvis fabriken</t>
       </text>
     </comment>
-    <comment ref="A23" authorId="5" shapeId="0" xr:uid="{E4E2B011-A98F-420C-969B-2FD7D9D7665D}">
+    <comment ref="A22" authorId="5" shapeId="0" xr:uid="{E4E2B011-A98F-420C-969B-2FD7D9D7665D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -104,7 +104,7 @@
     Behöver vara unikt för följesedeln</t>
       </text>
     </comment>
-    <comment ref="A52" authorId="6" shapeId="0" xr:uid="{A86F878F-4E99-41E0-9D3A-82CB4E3ADFB1}">
+    <comment ref="A51" authorId="6" shapeId="0" xr:uid="{A86F878F-4E99-41E0-9D3A-82CB4E3ADFB1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -112,7 +112,7 @@
     Har inte hittat en lämplig dimension, kräver change request till Peppol.</t>
       </text>
     </comment>
-    <comment ref="A53" authorId="7" shapeId="0" xr:uid="{742EB100-CD78-456B-B0BA-734D6E845950}">
+    <comment ref="A52" authorId="7" shapeId="0" xr:uid="{742EB100-CD78-456B-B0BA-734D6E845950}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -120,7 +120,7 @@
     Naturliga basen är den yta som är nedåt när elementet är monterat.</t>
       </text>
     </comment>
-    <comment ref="A58" authorId="8" shapeId="0" xr:uid="{E13F7F03-4213-4DED-B75C-E3E7A36417DD}">
+    <comment ref="A57" authorId="8" shapeId="0" xr:uid="{E13F7F03-4213-4DED-B75C-E3E7A36417DD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -128,7 +128,7 @@
     Räknas in i byggnadens GWP/BTA</t>
       </text>
     </comment>
-    <comment ref="A66" authorId="9" shapeId="0" xr:uid="{7FF3A7FC-3F77-48B3-B460-BEAC7C6C356C}">
+    <comment ref="A65" authorId="9" shapeId="0" xr:uid="{7FF3A7FC-3F77-48B3-B460-BEAC7C6C356C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -136,7 +136,7 @@
     Går att räkna ut från de enskilda elementen.</t>
       </text>
     </comment>
-    <comment ref="A67" authorId="10" shapeId="0" xr:uid="{8D583249-D2B9-4BB3-ADA1-C52BCC0D4924}">
+    <comment ref="A66" authorId="10" shapeId="0" xr:uid="{8D583249-D2B9-4BB3-ADA1-C52BCC0D4924}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -144,7 +144,7 @@
     Går att räkna ut från de enskilda elementen</t>
       </text>
     </comment>
-    <comment ref="B68" authorId="11" shapeId="0" xr:uid="{C4E333B8-071B-42E6-A955-8C620D720973}">
+    <comment ref="B67" authorId="11" shapeId="0" xr:uid="{C4E333B8-071B-42E6-A955-8C620D720973}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -152,7 +152,7 @@
     Behöver ett tydligt exempel</t>
       </text>
     </comment>
-    <comment ref="B73" authorId="12" shapeId="0" xr:uid="{CD81EBB4-26FB-475E-BC7E-B6153C724302}">
+    <comment ref="B72" authorId="12" shapeId="0" xr:uid="{CD81EBB4-26FB-475E-BC7E-B6153C724302}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -162,7 +162,7 @@
     Diskussionspunkt, ligger på första item</t>
       </text>
     </comment>
-    <comment ref="B74" authorId="13" shapeId="0" xr:uid="{25E323A3-E4B6-4F80-91F3-E85CCAD8C428}">
+    <comment ref="B73" authorId="13" shapeId="0" xr:uid="{25E323A3-E4B6-4F80-91F3-E85CCAD8C428}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="223">
   <si>
     <t>Elementnamn</t>
   </si>
@@ -821,9 +821,6 @@
     <t>cac:Shipment/cac:Delivery/cac:DeliveryLocation/cac:Address/cac:LocationCoordinate</t>
   </si>
   <si>
-    <t>cbc:CompanyID</t>
-  </si>
-  <si>
     <t>cac:PostalAddress</t>
   </si>
   <si>
@@ -848,9 +845,6 @@
     <t>cac:StandardItemIdentification</t>
   </si>
   <si>
-    <t>Separera med #</t>
-  </si>
-  <si>
     <t>cac:AdditionalItemProperty BoVResourceID</t>
   </si>
   <si>
@@ -882,13 +876,25 @@
   </si>
   <si>
     <t>cac:AdditionalItemProperty GrossArea</t>
+  </si>
+  <si>
+    <t>cac:PartyIdentification</t>
+  </si>
+  <si>
+    <t>cbc:CompanyID och</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separera med # </t>
+  </si>
+  <si>
+    <t>schemeID="0160"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -930,12 +936,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -1034,7 +1034,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1050,8 +1050,8 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1402,43 +1402,43 @@
   <threadedComment ref="A4" dT="2025-06-03T13:55:33.14" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{414081A2-CA42-4F60-B66B-791B6B91BE8C}">
     <text>Behöver inte ha med denna men kan skicka med det om entreprenörerna vill.</text>
   </threadedComment>
-  <threadedComment ref="A10" dT="2025-10-01T09:10:06.33" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{B54A39DE-43A5-43E4-8551-D38ABB14315B}">
+  <threadedComment ref="A9" dT="2025-10-01T09:10:06.33" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{B54A39DE-43A5-43E4-8551-D38ABB14315B}">
     <text>Behöver komma överens i projektet vilken adress-rad man ska använda.</text>
   </threadedComment>
-  <threadedComment ref="A15" dT="2025-10-01T09:11:34.57" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{3D75DFE4-9945-4CD7-B835-1AB81FDE3917}">
+  <threadedComment ref="A14" dT="2025-10-01T09:11:34.57" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{3D75DFE4-9945-4CD7-B835-1AB81FDE3917}">
     <text>Behöver vara obligatorisk</text>
   </threadedComment>
-  <threadedComment ref="A20" dT="2025-10-01T09:25:57.03" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{21029AF8-9FD7-40BA-AF0F-C67FA4AF6DED}">
+  <threadedComment ref="A19" dT="2025-10-01T09:25:57.03" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{21029AF8-9FD7-40BA-AF0F-C67FA4AF6DED}">
     <text>Relevant kontaktperson , inte nödvändigtvis fabriken</text>
   </threadedComment>
-  <threadedComment ref="A23" dT="2025-10-01T09:28:07.10" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{E4E2B011-A98F-420C-969B-2FD7D9D7665D}">
+  <threadedComment ref="A22" dT="2025-10-01T09:28:07.10" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{E4E2B011-A98F-420C-969B-2FD7D9D7665D}">
     <text>Behöver vara unikt för följesedeln</text>
   </threadedComment>
-  <threadedComment ref="A52" dT="2025-11-14T09:09:38.43" personId="{754BC36D-856B-4183-8CB4-20C034C3A08D}" id="{A86F878F-4E99-41E0-9D3A-82CB4E3ADFB1}" done="1">
+  <threadedComment ref="A51" dT="2025-11-14T09:09:38.43" personId="{754BC36D-856B-4183-8CB4-20C034C3A08D}" id="{A86F878F-4E99-41E0-9D3A-82CB4E3ADFB1}" done="1">
     <text>Har inte hittat en lämplig dimension, kräver change request till Peppol.</text>
   </threadedComment>
-  <threadedComment ref="A53" dT="2025-06-04T08:30:43.56" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{742EB100-CD78-456B-B0BA-734D6E845950}">
+  <threadedComment ref="A52" dT="2025-06-04T08:30:43.56" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{742EB100-CD78-456B-B0BA-734D6E845950}">
     <text>Naturliga basen är den yta som är nedåt när elementet är monterat.</text>
   </threadedComment>
-  <threadedComment ref="A58" dT="2025-06-03T13:15:19.58" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{E13F7F03-4213-4DED-B75C-E3E7A36417DD}">
+  <threadedComment ref="A57" dT="2025-06-03T13:15:19.58" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{E13F7F03-4213-4DED-B75C-E3E7A36417DD}">
     <text>Räknas in i byggnadens GWP/BTA</text>
   </threadedComment>
-  <threadedComment ref="A66" dT="2025-10-24T09:25:21.50" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{7FF3A7FC-3F77-48B3-B460-BEAC7C6C356C}">
+  <threadedComment ref="A65" dT="2025-10-24T09:25:21.50" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{7FF3A7FC-3F77-48B3-B460-BEAC7C6C356C}">
     <text>Går att räkna ut från de enskilda elementen.</text>
   </threadedComment>
-  <threadedComment ref="A67" dT="2025-10-24T09:25:30.49" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{8D583249-D2B9-4BB3-ADA1-C52BCC0D4924}">
+  <threadedComment ref="A66" dT="2025-10-24T09:25:30.49" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{8D583249-D2B9-4BB3-ADA1-C52BCC0D4924}">
     <text>Går att räkna ut från de enskilda elementen</text>
   </threadedComment>
-  <threadedComment ref="B68" dT="2025-11-14T09:21:09.24" personId="{754BC36D-856B-4183-8CB4-20C034C3A08D}" id="{C4E333B8-071B-42E6-A955-8C620D720973}" done="1">
+  <threadedComment ref="B67" dT="2025-11-14T09:21:09.24" personId="{754BC36D-856B-4183-8CB4-20C034C3A08D}" id="{C4E333B8-071B-42E6-A955-8C620D720973}" done="1">
     <text>Behöver ett tydligt exempel</text>
   </threadedComment>
-  <threadedComment ref="B73" dT="2025-10-24T09:43:12.41" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{CD81EBB4-26FB-475E-BC7E-B6153C724302}" done="1">
+  <threadedComment ref="B72" dT="2025-10-24T09:43:12.41" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{CD81EBB4-26FB-475E-BC7E-B6153C724302}" done="1">
     <text>Innehåller både datum och tid</text>
   </threadedComment>
-  <threadedComment ref="B73" dT="2025-11-14T09:25:29.34" personId="{754BC36D-856B-4183-8CB4-20C034C3A08D}" id="{4E5346C9-D825-4545-83E6-D51FDD8D6829}" parentId="{CD81EBB4-26FB-475E-BC7E-B6153C724302}">
+  <threadedComment ref="B72" dT="2025-11-14T09:25:29.34" personId="{754BC36D-856B-4183-8CB4-20C034C3A08D}" id="{4E5346C9-D825-4545-83E6-D51FDD8D6829}" parentId="{CD81EBB4-26FB-475E-BC7E-B6153C724302}">
     <text>Diskussionspunkt, ligger på första item</text>
   </threadedComment>
-  <threadedComment ref="B74" dT="2025-10-24T09:43:18.26" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{25E323A3-E4B6-4F80-91F3-E85CCAD8C428}">
+  <threadedComment ref="B73" dT="2025-10-24T09:43:18.26" personId="{1CC54AC4-20B9-42D9-90F5-C03AFAE9BE19}" id="{25E323A3-E4B6-4F80-91F3-E85CCAD8C428}">
     <text>Innehåller både datum och tid</text>
   </threadedComment>
 </ThreadedComments>
@@ -1446,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3345FADF-F970-4D25-95E9-2F699A3AE5F1}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="70.3984375" bestFit="1" customWidth="1"/>
@@ -1468,10 +1468,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>77</v>
@@ -1482,7 +1482,10 @@
         <v>78</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>200</v>
+        <v>220</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>219</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>79</v>
@@ -1490,10 +1493,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>203</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>204</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>80</v>
@@ -1504,7 +1507,10 @@
         <v>81</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>200</v>
+        <v>220</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -1512,7 +1518,7 @@
         <v>82</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -1520,7 +1526,7 @@
         <v>83</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -1536,375 +1542,387 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="7" t="s">
-        <v>89</v>
+      <c r="A12" t="s">
+        <v>91</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>91</v>
+      <c r="A13" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="7" t="s">
-        <v>93</v>
+      <c r="A14" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="C14" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" s="8" t="s">
-        <v>95</v>
+      <c r="A15" t="s">
+        <v>98</v>
       </c>
       <c r="B15" t="s">
         <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" t="s">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>112</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>206</v>
+        <v>113</v>
+      </c>
+      <c r="B23" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>115</v>
+      <c r="A25" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="B25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" s="7" t="s">
-        <v>119</v>
+      <c r="A27" t="s">
+        <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B28" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>123</v>
+      <c r="A29" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A30" s="7" t="s">
-        <v>125</v>
+      <c r="A30" t="s">
+        <v>127</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B31" t="s">
-        <v>198</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="B33" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>131</v>
+      <c r="A34" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B35" t="s">
-        <v>134</v>
-      </c>
+      <c r="A35" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="6"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B36" s="6"/>
+      <c r="A36" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" t="s">
+        <v>221</v>
+      </c>
+      <c r="D36" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A37" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="C37" t="s">
-        <v>209</v>
+      <c r="A37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
+      <c r="A38" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
         <v>136</v>
       </c>
-      <c r="B38" t="s">
-        <v>137</v>
-      </c>
-      <c r="E38" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="B39" t="s">
-        <v>140</v>
-      </c>
-      <c r="E39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>143</v>
-      </c>
-      <c r="B41" t="s">
-        <v>210</v>
+      <c r="A41" s="10" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="10" t="s">
-        <v>144</v>
+      <c r="A42" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B45" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B46" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B47" t="s">
-        <v>215</v>
+        <v>214</v>
+      </c>
+      <c r="D47" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B48" t="s">
-        <v>216</v>
-      </c>
-      <c r="D48" t="s">
-        <v>65</v>
+        <v>215</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B49" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B50" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>154</v>
+      </c>
+      <c r="B51" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A51" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B51" t="s">
-        <v>219</v>
+      <c r="D51" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B52" t="s">
-        <v>220</v>
+        <v>157</v>
+      </c>
+      <c r="C52" t="s">
+        <v>158</v>
       </c>
       <c r="D52" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B53" t="s">
         <v>157</v>
       </c>
       <c r="C53" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D53" t="s">
         <v>159</v>
@@ -1912,13 +1930,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B54" t="s">
         <v>157</v>
       </c>
       <c r="C54" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D54" t="s">
         <v>159</v>
@@ -1926,123 +1944,125 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B55" t="s">
         <v>157</v>
       </c>
       <c r="C55" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D55" t="s">
-        <v>159</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>164</v>
-      </c>
-      <c r="B56" t="s">
-        <v>157</v>
-      </c>
-      <c r="C56" t="s">
-        <v>165</v>
-      </c>
-      <c r="D56" t="s">
-        <v>65</v>
-      </c>
+      <c r="A56" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B56" s="6"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A57" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B57" s="6"/>
+      <c r="A57" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B58" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B59" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B60" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
+        <v>157</v>
+      </c>
+      <c r="C61" t="s">
+        <v>175</v>
+      </c>
+      <c r="D61" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A62" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B62" t="s">
-        <v>157</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="A62" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B62" s="6"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A63" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B63" t="s">
+        <v>178</v>
+      </c>
+      <c r="C63" t="s">
         <v>175</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D63" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A63" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B63" s="6"/>
-    </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A64" s="7" t="s">
-        <v>177</v>
+      <c r="A64" t="s">
+        <v>179</v>
       </c>
       <c r="B64" t="s">
-        <v>178</v>
-      </c>
-      <c r="C64" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D64" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>179</v>
-      </c>
-      <c r="B65" t="s">
-        <v>180</v>
-      </c>
-      <c r="D65" t="s">
-        <v>32</v>
-      </c>
+      <c r="A65" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
+      <c r="C66" s="11" t="s">
+        <v>165</v>
+      </c>
       <c r="D66" s="11" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="E66" s="11"/>
       <c r="F66" s="11"/>
@@ -2050,79 +2070,63 @@
       <c r="H66" s="11"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A67" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11"/>
+      <c r="A67" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B67" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B68" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
+      </c>
+      <c r="B69" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A70" s="7" t="s">
-        <v>186</v>
+      <c r="A70" s="9" t="s">
+        <v>187</v>
       </c>
       <c r="B70" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B71" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="B72" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A74" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
+      <c r="A74" t="s">
         <v>195</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B74" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2134,11 +2138,13 @@
     <hyperlink ref="B6" r:id="rId4" display="https://bis.beast.se/syntax/AdvancedDespatchAdvice/cac-DeliveryCustomerParty/cac-Party/cac-PartyLegalEntity/cbc-RegistrationName/" xr:uid="{9387A765-C91A-4473-BB1C-160AA1BFA18E}"/>
     <hyperlink ref="B7" r:id="rId5" display="https://bis.beast.se/syntax/AdvancedDespatchAdvice/cac-DeliveryCustomerParty/cac-Party/cbc-EndpointID/" xr:uid="{F21E248E-FA21-457F-B941-FB13B5E1517F}"/>
     <hyperlink ref="B4" r:id="rId6" display="https://bis.beast.se/syntax/AdvancedDespatchAdvice/cac-SellerSupplierParty/cac-Party/cac-PartyLegalEntity/cbc-RegistrationName/" xr:uid="{FEAB4B15-5E62-4C67-8A4F-D1ADFCCD9292}"/>
-    <hyperlink ref="B23" r:id="rId7" display="https://bis.beast.se/syntax/AdvancedDespatchAdvice/cbc-ID/" xr:uid="{5C710DEB-6B8C-4042-912B-08128ED9F606}"/>
-    <hyperlink ref="B37" r:id="rId8" display="https://bis.beast.se/syntax/AdvancedDespatchAdvice/cac-DespatchLine/cac-Item/cac-StandardItemIdentification/" xr:uid="{727739BB-5C22-478B-A4C6-29E349E34FA3}"/>
+    <hyperlink ref="B22" r:id="rId7" display="https://bis.beast.se/syntax/AdvancedDespatchAdvice/cbc-ID/" xr:uid="{5C710DEB-6B8C-4042-912B-08128ED9F606}"/>
+    <hyperlink ref="B36" r:id="rId8" display="https://bis.beast.se/syntax/AdvancedDespatchAdvice/cac-DespatchLine/cac-Item/cac-StandardItemIdentification/" xr:uid="{727739BB-5C22-478B-A4C6-29E349E34FA3}"/>
+    <hyperlink ref="C5" r:id="rId9" display="https://bis.beast.se/syntax/AdvancedDespatchAdvice/cac-DespatchSupplierParty/cac-Party/cac-PartyIdentification/" xr:uid="{697D17E5-623D-4109-84E5-8A5A8642FD35}"/>
+    <hyperlink ref="C3" r:id="rId10" display="https://bis.beast.se/syntax/AdvancedDespatchAdvice/cac-SellerSupplierParty/cac-Party/cac-PartyIdentification/" xr:uid="{E94BD1A0-AE39-47C0-A2B0-F79ADA4399A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId9"/>
+  <legacyDrawing r:id="rId11"/>
 </worksheet>
 </file>
 
@@ -2964,26 +2970,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8ccd7eff-ff94-4947-899c-fce55dd2f55c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8f9d2b4d-7247-41d6-b807-747488ee234f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100171F2C78FC24AA49A33C1A304F9B6BED" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="40f1c6a9c3369aec39ef7f2057bcc08e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8f9d2b4d-7247-41d6-b807-747488ee234f" xmlns:ns3="8ccd7eff-ff94-4947-899c-fce55dd2f55c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0b0cce8411b154a57b1c79d4b3bcfc2d" ns2:_="" ns3:_="">
     <xsd:import namespace="8f9d2b4d-7247-41d6-b807-747488ee234f"/>
@@ -3218,13 +3204,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8ccd7eff-ff94-4947-899c-fce55dd2f55c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8f9d2b4d-7247-41d6-b807-747488ee234f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BA2354-9C1D-4686-A177-67E6339D2F15}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D42C254-CCF7-4C40-A2FB-0ACF47A056E6}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8f9d2b4d-7247-41d6-b807-747488ee234f"/>
+    <ds:schemaRef ds:uri="8ccd7eff-ff94-4947-899c-fce55dd2f55c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9152604a-f0cc-467d-b221-c1d9d3891a16"/>
-    <ds:schemaRef ds:uri="041a38dd-b05d-41ec-a780-98c9cef43fb4"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3238,5 +3252,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D42C254-CCF7-4C40-A2FB-0ACF47A056E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BA2354-9C1D-4686-A177-67E6339D2F15}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9152604a-f0cc-467d-b221-c1d9d3891a16"/>
+    <ds:schemaRef ds:uri="041a38dd-b05d-41ec-a780-98c9cef43fb4"/>
+    <ds:schemaRef ds:uri="8ccd7eff-ff94-4947-899c-fce55dd2f55c"/>
+    <ds:schemaRef ds:uri="8f9d2b4d-7247-41d6-b807-747488ee234f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>